--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3333333333333333</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="B2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.625</v>
+        <v>0.4460431654676259</v>
       </c>
       <c r="D2">
-        <v>0.6</v>
+        <v>0.6581196581196581</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.1-8B-Instruct/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.8888888888888888</v>
+        <v>0.8979591836734694</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="C2">
-        <v>0.4460431654676259</v>
+        <v>0.4710144927536232</v>
       </c>
       <c r="D2">
-        <v>0.6581196581196581</v>
+        <v>0.6134453781512605</v>
       </c>
       <c r="E2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
